--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -2,18 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\54\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F5AC0B1-359C-427B-8176-9FBEFFD9442B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E766F55-B2AC-4054-9295-38B6E215697D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DF33B88C-4786-4377-BF23-5EC579C56E55}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DF33B88C-4786-4377-BF23-5EC579C56E55}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,8 +34,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="132">
   <si>
     <t>#year</t>
   </si>
@@ -78,12 +101,6 @@
     <t xml:space="preserve">Anjith </t>
   </si>
   <si>
-    <t>ABCDEF-2005-00idjifoji</t>
-  </si>
-  <si>
-    <t>ABCDEF-2005-hdfffddf</t>
-  </si>
-  <si>
     <t>Column1</t>
   </si>
   <si>
@@ -93,15 +110,6 @@
     <t>aanbbjhbs</t>
   </si>
   <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Running Total</t>
-  </si>
-  <si>
     <t>Count</t>
   </si>
   <si>
@@ -112,13 +120,346 @@
   </si>
   <si>
     <t>Column5</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>One plus</t>
+  </si>
+  <si>
+    <t>Razer</t>
+  </si>
+  <si>
+    <t>ios</t>
+  </si>
+  <si>
+    <t>Vivo</t>
+  </si>
+  <si>
+    <t>Microsoft</t>
+  </si>
+  <si>
+    <t>Canon</t>
+  </si>
+  <si>
+    <t>Kotak</t>
+  </si>
+  <si>
+    <t>Axis</t>
+  </si>
+  <si>
+    <t>Miamia</t>
+  </si>
+  <si>
+    <t>Mobile</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Fruits</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>#index</t>
+  </si>
+  <si>
+    <t>Vlookup</t>
+  </si>
+  <si>
+    <t>Marks</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Agecriteria</t>
+  </si>
+  <si>
+    <t>maths</t>
+  </si>
+  <si>
+    <t>physics</t>
+  </si>
+  <si>
+    <t>Analysis(OR)</t>
+  </si>
+  <si>
+    <t>Analysis(AND)</t>
+  </si>
+  <si>
+    <t>Result(OR)</t>
+  </si>
+  <si>
+    <t>Result(And)</t>
+  </si>
+  <si>
+    <t>XOR</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>surname</t>
+  </si>
+  <si>
+    <t>credits</t>
+  </si>
+  <si>
+    <t>Geography</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>StudentID</t>
+  </si>
+  <si>
+    <t>StudyHoursPerWeek</t>
+  </si>
+  <si>
+    <t>AttendancePct</t>
+  </si>
+  <si>
+    <t>SleepHours</t>
+  </si>
+  <si>
+    <t>TestScore</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Science</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>Commerce</t>
+  </si>
+  <si>
+    <t>Arts</t>
+  </si>
+  <si>
+    <t>Malhotra</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Patel</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Jain</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Singh</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Chopra</t>
+  </si>
+  <si>
+    <t>Mehta</t>
+  </si>
+  <si>
+    <t>Yadav</t>
+  </si>
+  <si>
+    <t>Iyer</t>
+  </si>
+  <si>
+    <t>Saxena</t>
+  </si>
+  <si>
+    <t>Joshi</t>
+  </si>
+  <si>
+    <t>Verma</t>
+  </si>
+  <si>
+    <t>Mishra</t>
+  </si>
+  <si>
+    <t>Reddy</t>
+  </si>
+  <si>
+    <t>Bose</t>
+  </si>
+  <si>
+    <t>Gupta</t>
+  </si>
+  <si>
+    <t>Kulkarni</t>
+  </si>
+  <si>
+    <t>Nair</t>
+  </si>
+  <si>
+    <t>Das</t>
+  </si>
+  <si>
+    <t>Kapoor</t>
+  </si>
+  <si>
+    <t>Sharma</t>
+  </si>
+  <si>
+    <t>Sno</t>
+  </si>
+  <si>
+    <t>Counta</t>
+  </si>
+  <si>
+    <t>Countifs</t>
+  </si>
+  <si>
+    <t>Countif</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>standard deviation  S</t>
+  </si>
+  <si>
+    <t>Standard deviation P</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>Variance P</t>
+  </si>
+  <si>
+    <t>Variance S</t>
+  </si>
+  <si>
+    <t>count blanks</t>
+  </si>
+  <si>
+    <t>correlation</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Logo</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Crunchyroll</t>
+  </si>
+  <si>
+    <t>Netflix</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,8 +482,65 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="5" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="5" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,6 +550,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF2F8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -164,23 +592,140 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="40% - Accent1" xfId="2" builtinId="31"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF1F4E78"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF2F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF2F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF2F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF2F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF2F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF2F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF2F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF2F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFEAF2F8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -193,6 +738,398 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1152525</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2457450</xdr:colOff>
+      <xdr:row>195</xdr:row>
+      <xdr:rowOff>1038225</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D43E5FB4-90C3-E83A-D794-91F3E6350E31}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+            <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5419725" y="39328725"/>
+          <a:ext cx="1304925" cy="819150"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>223</xdr:row>
+      <xdr:rowOff>180976</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3486150" cy="547530"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A286711-8B09-AD97-5427-9163D84CBA0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3171825" y="42033826"/>
+          <a:ext cx="3486150" cy="547530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="900"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>148661</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3171825</xdr:colOff>
+      <xdr:row>196</xdr:row>
+      <xdr:rowOff>1020866</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{43A75FC4-4F0F-4785-70D4-D539F958BB1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+            <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4733925" y="38115311"/>
+          <a:ext cx="2705100" cy="872205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>64770</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7772400" cy="233205"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="TextBox 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B5D1BA76-84BB-26C5-A21C-F7BFE6E92B65}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3171825" y="42317670"/>
+          <a:ext cx="7772400" cy="233205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="900"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>523874</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2946400</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>1057275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E873758-70FD-B216-8A0C-693A5FC4A4DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+            <a:ext uri="{837473B0-CC2E-450A-ABE3-18F120FF3D39}">
+              <a1611:picAttrSrcUrl xmlns:a1611="http://schemas.microsoft.com/office/drawing/2016/11/main" r:id="rId6"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="26123" r="29388"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4791074" y="39233475"/>
+          <a:ext cx="2422526" cy="933450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>197</xdr:row>
+      <xdr:rowOff>1916430</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7772400" cy="233205"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="TextBox 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F7B63DA-AB78-6F6F-6382-45BE8864C7E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4410075" y="41026080"/>
+          <a:ext cx="7772400" cy="233205"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-IN" sz="900"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>3390899</xdr:colOff>
+      <xdr:row>198</xdr:row>
+      <xdr:rowOff>904876</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18" descr="Netflix Starting From $6.99 a Month ...">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7145FB7-531F-67E4-7BF4-2A9F8C789177}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="-1332" t="7792" r="667" b="10390"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="4781550" y="41605200"/>
+          <a:ext cx="2876549" cy="600076"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E5EDC68-C247-451E-8E3C-9F9B9BC0E9B5}" name="Table1" displayName="Table1" ref="K4:L8" totalsRowShown="0">
   <autoFilter ref="K4:L8" xr:uid="{1E5EDC68-C247-451E-8E3C-9F9B9BC0E9B5}"/>
@@ -201,6 +1138,83 @@
     <tableColumn id="2" xr3:uid="{3C2EE68C-24C1-4413-B1D5-6178FF733525}" name="Column2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{55C63175-66D4-4B95-A68D-AD7DAFF90E19}" name="Table10" displayName="Table10" ref="J31:K34" totalsRowShown="0">
+  <autoFilter ref="J31:K34" xr:uid="{55C63175-66D4-4B95-A68D-AD7DAFF90E19}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{4B7F6420-4B5A-433B-AF45-9CF3CF9A3C1B}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{17223A37-06EF-4C0E-89E9-BD6FC175F38F}" name="Column2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{32D6E0C1-45DF-4E9C-8764-651C4FDB6A1B}" name="Table11" displayName="Table11" ref="E37:F40" totalsRowCount="1">
+  <autoFilter ref="E37:F39" xr:uid="{32D6E0C1-45DF-4E9C-8764-651C4FDB6A1B}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{80292359-138F-4FDC-8042-03BFE56D8134}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{7306C8A6-BD33-4637-A14B-9091FEBB186D}" name="Column2">
+      <calculatedColumnFormula>INDEX(F17:H26,3,3)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{6D23AEC7-BB81-47EE-A581-EA940653D7F7}" name="Table12" displayName="Table12" ref="E47:G54" totalsRowShown="0">
+  <autoFilter ref="E47:G54" xr:uid="{6D23AEC7-BB81-47EE-A581-EA940653D7F7}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{25016839-FA58-4261-BA9F-881DBC01AF28}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{1E07C8DA-F0BD-4A03-9AE7-0AF9BF69555E}" name="Marks"/>
+    <tableColumn id="3" xr3:uid="{E396C68F-0D29-4A5B-A6E8-26F951B3BCCC}" name="Result">
+      <calculatedColumnFormula>IF(F48&lt;35,"Fail","Pass")</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{49FA1AE4-07E8-4B83-BBC3-5B0C11906E13}" name="StatisticalDataset" displayName="StatisticalDataset" ref="V1:AC31" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="V1:AC31" xr:uid="{49FA1AE4-07E8-4B83-BBC3-5B0C11906E13}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{14D47D12-3184-440B-A187-42FDEA39CAB7}" name="StudentID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{19EB2A54-921E-4BFD-A38E-9C95CB6C8FCE}" name="Age" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{50AE5DE0-FB30-4C94-AC17-036C328871D7}" name="Gender" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{CD00E9E4-171A-43CC-AF22-A6B6AD56332A}" name="StudyHoursPerWeek" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{811C6413-3EAA-4CA6-9A59-43C6CC861E15}" name="AttendancePct" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{2EF25E21-E382-47C2-80A5-C1B14E651671}" name="SleepHours" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{8B79AB12-F22D-43C1-A6C6-D2E2D1F016C4}" name="TestScore" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{317D2FEE-AE7E-4D6F-AB80-C3ADF7F5A6A6}" name="Department" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{CD12296C-B767-4D3E-A979-5F96755E182B}" name="Table14" displayName="Table14" ref="I77:J90" totalsRowShown="0">
+  <autoFilter ref="I77:J90" xr:uid="{CD12296C-B767-4D3E-A979-5F96755E182B}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{B6139D03-F902-4F01-8B01-ABB8540ACD54}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{05CE50D0-F2B6-4C5B-929F-5AFA39245436}" name="Column2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{132428D0-4D74-4705-B7D6-B06F5A2A72CD}" name="Table18" displayName="Table18" ref="E195:G199" headerRowCount="0">
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{D007325C-797A-4475-A34A-E479CB62A44F}" name="Column1" totalsRowLabel="Total"/>
+    <tableColumn id="2" xr3:uid="{757BC367-F0BE-4DCE-8EA9-631FECBB5B34}" name="Column2"/>
+    <tableColumn id="3" xr3:uid="{C8FA9210-7708-42BC-82BF-950953FE6D7B}" name="Column3" totalsRowFunction="count"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -239,6 +1253,74 @@
     <tableColumn id="5" xr3:uid="{CF7AA54D-228C-4002-AF41-0E3C768953D2}" name="Column5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F971CF5D-F152-4445-A495-4A6DB68494E6}" name="Table5" displayName="Table5" ref="E17:H27" totalsRowShown="0">
+  <autoFilter ref="E17:H27" xr:uid="{F971CF5D-F152-4445-A495-4A6DB68494E6}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{7E81C7FA-38B9-405F-9E06-2CAAE0ACBD60}" name="Number"/>
+    <tableColumn id="2" xr3:uid="{4BF4B385-C77A-4D4F-996A-E5B564F39353}" name="Description"/>
+    <tableColumn id="3" xr3:uid="{F530EF87-C720-44A1-A227-7187A5D43E24}" name="Type"/>
+    <tableColumn id="4" xr3:uid="{57AD224E-A922-4C77-A9B9-83493F7137D5}" name="Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{5A9F558B-DBA3-40C6-A3C5-9CF851107A5E}" name="Table6" displayName="Table6" ref="J25:T28" totalsRowShown="0">
+  <autoFilter ref="J25:T28" xr:uid="{5A9F558B-DBA3-40C6-A3C5-9CF851107A5E}"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{AD2C7051-0284-4DEB-883D-D3EE00049E62}" name="Number"/>
+    <tableColumn id="2" xr3:uid="{68FB7D43-C4D9-4370-B97A-683E8DB7DE32}" name="1"/>
+    <tableColumn id="3" xr3:uid="{4CA0C17E-8EC5-44EE-8088-69241B63A760}" name="2"/>
+    <tableColumn id="4" xr3:uid="{E9133917-BA2B-4706-92E5-B8524F854380}" name="3"/>
+    <tableColumn id="5" xr3:uid="{16C7DDEA-04FE-4656-A507-731164539A31}" name="4"/>
+    <tableColumn id="6" xr3:uid="{EC963952-3320-4D39-9D5B-6A2B296C97D7}" name="5"/>
+    <tableColumn id="7" xr3:uid="{411EF269-5EFD-4FE9-B8EA-2C31207D5BA8}" name="6"/>
+    <tableColumn id="8" xr3:uid="{175281EB-9FC4-4EE9-B22C-5ACE8EC09B9B}" name="7"/>
+    <tableColumn id="9" xr3:uid="{A0B557EB-152A-4883-8E42-FF3EDFD64D4C}" name="8"/>
+    <tableColumn id="10" xr3:uid="{F04244CD-F2FB-464B-8419-EEA95C6F8033}" name="9"/>
+    <tableColumn id="11" xr3:uid="{9D7A5ECC-195F-40CF-B358-8BD3194A3EA2}" name="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{CE3ECAE0-D2E7-491F-BAF6-CAECA5D9D47F}" name="Table7" displayName="Table7" ref="J36:K39" totalsRowShown="0">
+  <autoFilter ref="J36:K39" xr:uid="{CE3ECAE0-D2E7-491F-BAF6-CAECA5D9D47F}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{7934187E-6939-408B-985B-F3A372775611}" name="Fruits"/>
+    <tableColumn id="2" xr3:uid="{9CD93689-E3AE-4FD7-86A6-4EB80CD550A7}" name="Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{277E6B81-E392-4E5F-A4DF-A007CF4C3817}" name="Table8" displayName="Table8" ref="F30:G34" totalsRowShown="0">
+  <autoFilter ref="F30:G34" xr:uid="{277E6B81-E392-4E5F-A4DF-A007CF4C3817}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{0F93776F-3370-4AB9-85EB-DBA1A6EB5F3E}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{8DA2B46E-31C4-4E42-9EF2-98289A1CC7B9}" name="Column2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{75708C6C-353D-4015-BBC5-C7717CAC12D2}" name="Table9" displayName="Table9" ref="J42:K44" totalsRowShown="0">
+  <autoFilter ref="J42:K44" xr:uid="{75708C6C-353D-4015-BBC5-C7717CAC12D2}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{9839B447-E4F8-4B22-9684-DFBC5DFB4C07}" name="Column1"/>
+    <tableColumn id="2" xr3:uid="{CB06FE9D-9F29-450F-A294-C6B8D2FEC04F}" name="Column2" dataDxfId="10">
+      <calculatedColumnFormula>MATCH(J43,J37:J39,1)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight17" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -537,13 +1619,74 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{2D449090-2E5A-46C1-B52F-034193A61775}">
+  <we:reference id="wa200005502" version="1.0.0.13" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200005502" version="1.0.0.13" store="wa200005502" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="docId" value="&quot;KtlfpyHV4Dd6QKAyoNtMu&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CREATE_PROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8CF0616-D87B-4C3E-938E-A55E8F80C6EB}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D733B070-BAA1-4520-A10B-417077394372}">
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:AC209"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" customWidth="1"/>
+    <col min="6" max="6" width="56.5703125" customWidth="1"/>
+    <col min="7" max="7" width="37" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="23.42578125" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
@@ -552,9 +1695,17 @@
     <col min="14" max="14" width="11" customWidth="1"/>
     <col min="15" max="15" width="18.140625" customWidth="1"/>
     <col min="16" max="16" width="21.5703125" customWidth="1"/>
+    <col min="22" max="22" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,8 +1715,58 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V1" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="V2" s="6">
+        <v>1001</v>
+      </c>
+      <c r="W2" s="6">
+        <v>18</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y2" s="6">
+        <v>12</v>
+      </c>
+      <c r="Z2" s="7">
+        <v>92</v>
+      </c>
+      <c r="AA2" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="AB2" s="6">
+        <v>78</v>
+      </c>
+      <c r="AC2" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G3" s="3" t="s">
         <v>3</v>
       </c>
@@ -583,8 +1784,32 @@
       <c r="O3" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V3" s="6">
+        <v>1002</v>
+      </c>
+      <c r="W3" s="6">
+        <v>19</v>
+      </c>
+      <c r="X3" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y3" s="6">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="7">
+        <v>85</v>
+      </c>
+      <c r="AA3" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="AB3" s="6">
+        <v>69</v>
+      </c>
+      <c r="AC3" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -595,31 +1820,55 @@
         <v>5</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="V4" s="6">
+        <v>1003</v>
+      </c>
+      <c r="W4" s="6">
+        <v>20</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y4" s="6">
+        <v>15</v>
+      </c>
+      <c r="Z4" s="7">
+        <v>96</v>
+      </c>
+      <c r="AA4" s="6">
+        <v>7.9</v>
+      </c>
+      <c r="AB4" s="6">
+        <v>88</v>
+      </c>
+      <c r="AC4" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="G5" t="s">
         <v>10</v>
       </c>
@@ -643,8 +1892,32 @@
         <f>SEARCH("A",O6)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V5" s="6">
+        <v>1004</v>
+      </c>
+      <c r="W5" s="6">
+        <v>21</v>
+      </c>
+      <c r="X5" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>7</v>
+      </c>
+      <c r="Z5" s="7">
+        <v>74</v>
+      </c>
+      <c r="AA5" s="6">
+        <v>6.2</v>
+      </c>
+      <c r="AB5" s="6">
+        <v>61</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -686,8 +1959,32 @@
         <f>SEARCH("2",O6)</f>
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V6" s="6">
+        <v>1005</v>
+      </c>
+      <c r="W6" s="6">
+        <v>22</v>
+      </c>
+      <c r="X6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>11</v>
+      </c>
+      <c r="Z6" s="7">
+        <v>89</v>
+      </c>
+      <c r="AA6" s="6">
+        <v>7.1</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>75</v>
+      </c>
+      <c r="AC6" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="H7">
         <f>FIND("5",G6)</f>
         <v>11</v>
@@ -704,8 +2001,32 @@
         <f>SEARCH("E",O6)</f>
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V7" s="6">
+        <v>1006</v>
+      </c>
+      <c r="W7" s="6">
+        <v>18</v>
+      </c>
+      <c r="X7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y7" s="6">
+        <v>16</v>
+      </c>
+      <c r="Z7" s="7">
+        <v>98</v>
+      </c>
+      <c r="AA7" s="6">
+        <v>8</v>
+      </c>
+      <c r="AB7" s="6">
+        <v>91</v>
+      </c>
+      <c r="AC7" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -713,30 +2034,154 @@
         <f>SUBSTITUTE(L7,"A","Z")</f>
         <v>ZBCDEF-uhdefih-001</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V8" s="6">
+        <v>1007</v>
+      </c>
+      <c r="W8" s="6">
+        <v>19</v>
+      </c>
+      <c r="X8" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="7">
+        <v>80</v>
+      </c>
+      <c r="AA8" s="6">
+        <v>6.5</v>
+      </c>
+      <c r="AB8" s="6">
+        <v>66</v>
+      </c>
+      <c r="AC8" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="V9" s="6">
+        <v>1008</v>
+      </c>
+      <c r="W9" s="6">
+        <v>20</v>
+      </c>
+      <c r="X9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>13</v>
+      </c>
+      <c r="Z9" s="7">
+        <v>93</v>
+      </c>
+      <c r="AA9" s="6">
+        <v>7.2</v>
+      </c>
+      <c r="AB9" s="6">
+        <v>82</v>
+      </c>
+      <c r="AC9" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="L10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="N10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="O10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="V10" s="6">
+        <v>1009</v>
+      </c>
+      <c r="W10" s="6">
+        <v>21</v>
+      </c>
+      <c r="X10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>10</v>
+      </c>
+      <c r="Z10" s="7">
+        <v>87</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>6.9</v>
+      </c>
+      <c r="AB10" s="6">
+        <v>73</v>
+      </c>
+      <c r="AC10" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="V11" s="6">
+        <v>1010</v>
+      </c>
+      <c r="W11" s="6">
+        <v>22</v>
+      </c>
+      <c r="X11" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>6</v>
+      </c>
+      <c r="Z11" s="7">
+        <v>70</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>58</v>
+      </c>
+      <c r="AC11" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M12" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V12" s="6">
+        <v>1011</v>
+      </c>
+      <c r="W12" s="6">
+        <v>18</v>
+      </c>
+      <c r="X12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y12" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z12" s="7">
+        <v>95</v>
+      </c>
+      <c r="AA12" s="6">
+        <v>7.8</v>
+      </c>
+      <c r="AB12" s="6">
+        <v>86</v>
+      </c>
+      <c r="AC12" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="M13" t="s">
         <v>13</v>
       </c>
@@ -747,23 +2192,4134 @@
         <f>_xlfn.CONCAT(M13," ",N13)</f>
         <v>Anjith  Kumar</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="V13" s="6">
+        <v>1012</v>
+      </c>
+      <c r="W13" s="6">
+        <v>19</v>
+      </c>
+      <c r="X13" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>9</v>
+      </c>
+      <c r="Z13" s="7">
+        <v>83</v>
+      </c>
+      <c r="AA13" s="6">
+        <v>6.4</v>
+      </c>
+      <c r="AB13" s="6">
+        <v>67</v>
+      </c>
+      <c r="AC13" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="V14" s="6">
+        <v>1013</v>
+      </c>
+      <c r="W14" s="6">
+        <v>20</v>
+      </c>
+      <c r="X14" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>17</v>
+      </c>
+      <c r="Z14" s="7">
+        <v>99</v>
+      </c>
+      <c r="AA14" s="6">
+        <v>8.1</v>
+      </c>
+      <c r="AB14" s="6">
+        <v>94</v>
+      </c>
+      <c r="AC14" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="V15" s="6">
+        <v>1014</v>
+      </c>
+      <c r="W15" s="6">
+        <v>21</v>
+      </c>
+      <c r="X15" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="7">
+        <v>68</v>
+      </c>
+      <c r="AA15" s="6">
+        <v>5.9</v>
+      </c>
+      <c r="AB15" s="6">
+        <v>54</v>
+      </c>
+      <c r="AC15" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="P16" t="s">
+        <v>16</v>
+      </c>
+      <c r="V16" s="6">
+        <v>1015</v>
+      </c>
+      <c r="W16" s="6">
+        <v>22</v>
+      </c>
+      <c r="X16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>12</v>
+      </c>
+      <c r="Z16" s="7">
+        <v>90</v>
+      </c>
+      <c r="AA16" s="6">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="6">
+        <v>79</v>
+      </c>
+      <c r="AC16" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="V17" s="6">
+        <v>1016</v>
+      </c>
+      <c r="W17" s="6">
         <v>18</v>
       </c>
+      <c r="X17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y17" s="6">
+        <v>15</v>
+      </c>
+      <c r="Z17" s="7">
+        <v>97</v>
+      </c>
+      <c r="AA17" s="6">
+        <v>7.7</v>
+      </c>
+      <c r="AB17" s="6">
+        <v>89</v>
+      </c>
+      <c r="AC17" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18">
+        <v>10000</v>
+      </c>
+      <c r="V18" s="6">
+        <v>1017</v>
+      </c>
+      <c r="W18" s="6">
+        <v>19</v>
+      </c>
+      <c r="X18" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y18" s="6">
+        <v>7</v>
+      </c>
+      <c r="Z18" s="7">
+        <v>76</v>
+      </c>
+      <c r="AA18" s="6">
+        <v>6.1</v>
+      </c>
+      <c r="AB18" s="6">
+        <v>62</v>
+      </c>
+      <c r="AC18" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H19">
+        <v>50000</v>
+      </c>
+      <c r="V19" s="6">
+        <v>1018</v>
+      </c>
+      <c r="W19" s="6">
+        <v>20</v>
+      </c>
+      <c r="X19" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y19" s="6">
+        <v>11</v>
+      </c>
+      <c r="Z19" s="7">
+        <v>88</v>
+      </c>
+      <c r="AA19" s="6">
+        <v>7</v>
+      </c>
+      <c r="AB19" s="6">
+        <v>74</v>
+      </c>
+      <c r="AC19" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>28</v>
+      </c>
+      <c r="G20" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20">
+        <v>120000</v>
+      </c>
+      <c r="V20" s="6">
+        <v>1019</v>
+      </c>
+      <c r="W20" s="6">
+        <v>21</v>
+      </c>
+      <c r="X20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y20" s="6">
+        <v>13</v>
+      </c>
+      <c r="Z20" s="7">
+        <v>91</v>
+      </c>
+      <c r="AA20" s="6">
+        <v>7.4</v>
+      </c>
+      <c r="AB20" s="6">
+        <v>81</v>
+      </c>
+      <c r="AC20" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" t="s">
+        <v>36</v>
+      </c>
+      <c r="H21">
+        <v>50000</v>
+      </c>
+      <c r="V21" s="6">
+        <v>1020</v>
+      </c>
+      <c r="W21" s="6">
+        <v>22</v>
+      </c>
+      <c r="X21" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y21" s="6">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="7">
+        <v>79</v>
+      </c>
+      <c r="AA21" s="6">
+        <v>6.3</v>
+      </c>
+      <c r="AB21" s="6">
+        <v>65</v>
+      </c>
+      <c r="AC21" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E22">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s">
+        <v>36</v>
+      </c>
+      <c r="H22">
+        <v>45000</v>
+      </c>
+      <c r="V22" s="6">
+        <v>1021</v>
+      </c>
+      <c r="W22" s="6">
+        <v>18</v>
+      </c>
+      <c r="X22" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y22" s="6">
+        <v>16</v>
+      </c>
+      <c r="Z22" s="7">
+        <v>98</v>
+      </c>
+      <c r="AA22" s="6">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AB22" s="6">
+        <v>93</v>
+      </c>
+      <c r="AC22" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E23">
+        <v>6</v>
+      </c>
+      <c r="F23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23">
+        <v>130000</v>
+      </c>
+      <c r="V23" s="6">
+        <v>1022</v>
+      </c>
+      <c r="W23" s="6">
+        <v>19</v>
+      </c>
+      <c r="X23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y23" s="6">
+        <v>10</v>
+      </c>
+      <c r="Z23" s="7">
+        <v>86</v>
+      </c>
+      <c r="AA23" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="AB23" s="6">
+        <v>71</v>
+      </c>
+      <c r="AC23" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E24">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24">
+        <v>30000</v>
+      </c>
+      <c r="V24" s="6">
+        <v>1023</v>
+      </c>
+      <c r="W24" s="6">
+        <v>20</v>
+      </c>
+      <c r="X24" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y24" s="6">
+        <v>6</v>
+      </c>
+      <c r="Z24" s="7">
+        <v>72</v>
+      </c>
+      <c r="AA24" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="AB24" s="6">
+        <v>57</v>
+      </c>
+      <c r="AC24" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E25">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25">
+        <v>40000</v>
+      </c>
+      <c r="J25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" t="s">
+        <v>41</v>
+      </c>
+      <c r="L25" t="s">
+        <v>42</v>
+      </c>
+      <c r="M25" t="s">
+        <v>43</v>
+      </c>
+      <c r="N25" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25" t="s">
+        <v>45</v>
+      </c>
+      <c r="P25" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>47</v>
+      </c>
+      <c r="R25" t="s">
+        <v>48</v>
+      </c>
+      <c r="S25" t="s">
+        <v>49</v>
+      </c>
+      <c r="T25" t="s">
+        <v>50</v>
+      </c>
+      <c r="V25" s="6">
+        <v>1024</v>
+      </c>
+      <c r="W25" s="6">
+        <v>21</v>
+      </c>
+      <c r="X25" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y25" s="6">
+        <v>12</v>
+      </c>
+      <c r="Z25" s="7">
+        <v>90</v>
+      </c>
+      <c r="AA25" s="6">
+        <v>7.1</v>
+      </c>
+      <c r="AB25" s="6">
+        <v>77</v>
+      </c>
+      <c r="AC25" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E26">
+        <v>9</v>
+      </c>
+      <c r="F26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26">
+        <v>60000</v>
+      </c>
+      <c r="J26" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" t="s">
+        <v>27</v>
+      </c>
+      <c r="M26" t="s">
+        <v>28</v>
+      </c>
+      <c r="N26" t="s">
+        <v>29</v>
+      </c>
+      <c r="O26" t="s">
+        <v>30</v>
+      </c>
+      <c r="P26" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>32</v>
+      </c>
+      <c r="R26" t="s">
+        <v>33</v>
+      </c>
+      <c r="S26" t="s">
+        <v>34</v>
+      </c>
+      <c r="T26" t="s">
+        <v>35</v>
+      </c>
+      <c r="V26" s="6">
+        <v>1025</v>
+      </c>
+      <c r="W26" s="6">
+        <v>22</v>
+      </c>
+      <c r="X26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>9</v>
+      </c>
+      <c r="Z26" s="7">
+        <v>84</v>
+      </c>
+      <c r="AA26" s="6">
+        <v>6.6</v>
+      </c>
+      <c r="AB26" s="6">
+        <v>68</v>
+      </c>
+      <c r="AC26" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" t="s">
+        <v>36</v>
+      </c>
+      <c r="H27">
+        <v>50000</v>
+      </c>
+      <c r="J27" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" t="s">
+        <v>36</v>
+      </c>
+      <c r="L27" t="s">
+        <v>36</v>
+      </c>
+      <c r="M27" t="s">
+        <v>37</v>
+      </c>
+      <c r="N27" t="s">
+        <v>36</v>
+      </c>
+      <c r="O27" t="s">
+        <v>36</v>
+      </c>
+      <c r="P27" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>37</v>
+      </c>
+      <c r="R27" t="s">
+        <v>36</v>
+      </c>
+      <c r="S27" t="s">
+        <v>37</v>
+      </c>
+      <c r="T27" t="s">
+        <v>36</v>
+      </c>
+      <c r="V27" s="6">
+        <v>1026</v>
+      </c>
+      <c r="W27" s="6">
+        <v>18</v>
+      </c>
+      <c r="X27" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z27" s="7">
+        <v>94</v>
+      </c>
+      <c r="AA27" s="6">
+        <v>7.6</v>
+      </c>
+      <c r="AB27" s="6">
+        <v>85</v>
+      </c>
+      <c r="AC27" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="J28" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28">
+        <v>10000</v>
+      </c>
+      <c r="L28">
+        <v>50000</v>
+      </c>
+      <c r="M28">
+        <v>120000</v>
+      </c>
+      <c r="N28">
+        <v>50000</v>
+      </c>
+      <c r="O28">
+        <v>45000</v>
+      </c>
+      <c r="P28">
+        <v>130000</v>
+      </c>
+      <c r="Q28">
+        <v>30000</v>
+      </c>
+      <c r="R28">
+        <v>40000</v>
+      </c>
+      <c r="S28">
+        <v>60000</v>
+      </c>
+      <c r="T28">
+        <v>50000</v>
+      </c>
+      <c r="V28" s="6">
+        <v>1027</v>
+      </c>
+      <c r="W28" s="6">
+        <v>19</v>
+      </c>
+      <c r="X28" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>5</v>
+      </c>
+      <c r="Z28" s="7">
+        <v>69</v>
+      </c>
+      <c r="AA28" s="6">
+        <v>5.8</v>
+      </c>
+      <c r="AB28" s="6">
+        <v>55</v>
+      </c>
+      <c r="AC28" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="29" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="F29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="4"/>
+      <c r="V29" s="6">
+        <v>1028</v>
+      </c>
+      <c r="W29" s="6">
+        <v>20</v>
+      </c>
+      <c r="X29" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y29" s="6">
+        <v>13</v>
+      </c>
+      <c r="Z29" s="7">
+        <v>92</v>
+      </c>
+      <c r="AA29" s="6">
+        <v>7.3</v>
+      </c>
+      <c r="AB29" s="6">
+        <v>83</v>
+      </c>
+      <c r="AC29" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="F30" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>15</v>
+      </c>
+      <c r="V30" s="6">
+        <v>1029</v>
+      </c>
+      <c r="W30" s="6">
+        <v>21</v>
+      </c>
+      <c r="X30" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>11</v>
+      </c>
+      <c r="Z30" s="7">
+        <v>88</v>
+      </c>
+      <c r="AA30" s="6">
+        <v>7</v>
+      </c>
+      <c r="AB30" s="6">
+        <v>76</v>
+      </c>
+      <c r="AC30" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="F31" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" t="e">
+        <f>VLOOKUP(F23,F18:K32H27,3,0)</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="J31" t="s">
+        <v>14</v>
+      </c>
+      <c r="K31" t="s">
+        <v>15</v>
+      </c>
+      <c r="V31" s="6">
+        <v>1030</v>
+      </c>
+      <c r="W31" s="6">
+        <v>22</v>
+      </c>
+      <c r="X31" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y31" s="6">
+        <v>7</v>
+      </c>
+      <c r="Z31" s="7">
+        <v>75</v>
+      </c>
+      <c r="AA31" s="6">
+        <v>6</v>
+      </c>
+      <c r="AB31" s="6">
+        <v>60</v>
+      </c>
+      <c r="AC31" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="5:29" x14ac:dyDescent="0.25">
+      <c r="F32" t="s">
+        <v>27</v>
+      </c>
+      <c r="G32">
+        <f>VLOOKUP(F19,F18:H27,3,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="J32" t="s">
+        <v>29</v>
+      </c>
+      <c r="K32">
+        <f>HLOOKUP(N26,K26:T28,3,0)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="33" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="F33" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33">
+        <f>VLOOKUP(F25,F18:H27,3,0)</f>
+        <v>40000</v>
+      </c>
+      <c r="J33" t="s">
+        <v>34</v>
+      </c>
+      <c r="K33">
+        <f>HLOOKUP(S26,K26:T28,3,0)</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="34" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="F34" t="s">
+        <v>29</v>
+      </c>
+      <c r="G34">
+        <f>VLOOKUP(F21,F18:H27,3,0)</f>
+        <v>50000</v>
+      </c>
+      <c r="J34" t="s">
+        <v>27</v>
+      </c>
+      <c r="K34">
+        <f>HLOOKUP(L26,K26:T28,3,0)</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="36" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="J36" t="s">
+        <v>38</v>
+      </c>
+      <c r="K36" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36">
+        <f>_xlfn.XLOOKUP(F22,F18:F27,H18:H27)</f>
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="37" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37" t="s">
+        <v>15</v>
+      </c>
+      <c r="J37" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37">
+        <v>10</v>
+      </c>
+      <c r="M37" t="str" cm="1">
+        <f t="array" ref="M37:N37">_xlfn.XLOOKUP(J43,F18:F27,G18:H27,"Not found")</f>
+        <v>Mobile</v>
+      </c>
+      <c r="N37">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="38" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38">
+        <f>INDEX(F18:H27,2,3)</f>
+        <v>50000</v>
+      </c>
+      <c r="J38" t="s">
+        <v>39</v>
+      </c>
+      <c r="K38">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>51</v>
+      </c>
+      <c r="F39">
+        <f>INDEX(F18:H27,3,3)</f>
+        <v>120000</v>
+      </c>
+      <c r="J39" t="s">
+        <v>40</v>
+      </c>
+      <c r="K39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="J42" t="s">
+        <v>14</v>
+      </c>
+      <c r="K42" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="J43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43">
+        <f t="shared" ref="K43:K44" si="0">MATCH(J43,J37:J39,1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="5:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J44" t="s">
+        <v>40</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" t="s">
+        <v>53</v>
+      </c>
+      <c r="G47" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E48" t="s">
+        <v>55</v>
+      </c>
+      <c r="F48">
+        <v>90</v>
+      </c>
+      <c r="G48" t="str">
+        <f>IF(F48&lt;35,"Fail","Pass")</f>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="49" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E49" t="s">
+        <v>56</v>
+      </c>
+      <c r="F49">
+        <v>45</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" ref="G49:G54" si="1">IF(F49&lt;35,"Fail","Pass")</f>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="50" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E50" t="s">
+        <v>57</v>
+      </c>
+      <c r="F50">
+        <v>60</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="51" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E51" t="s">
+        <v>58</v>
+      </c>
+      <c r="F51">
+        <v>30</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="52" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E52" t="s">
+        <v>59</v>
+      </c>
+      <c r="F52">
+        <v>80</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="53" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E53" t="s">
+        <v>60</v>
+      </c>
+      <c r="F53">
+        <v>55</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="54" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E54" t="s">
+        <v>61</v>
+      </c>
+      <c r="F54">
+        <v>78</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="57" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E57" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E58">
+        <v>78</v>
+      </c>
+      <c r="F58" t="str">
+        <f>IF(E58&gt;=80,"Above 80",IF(E58&gt;=70,"Above 70",IF(E58&gt;=60,"Above 60",IF(E58&gt;=50,"Above 50","Under 50"))))</f>
+        <v>Above 70</v>
+      </c>
+      <c r="G58" t="str" cm="1">
+        <f t="array" ref="G58">_xlfn.IFS(E58&gt;=80,"Above 80",E58&gt;=70,"Above 70",E58&gt;=60,"Above 60",E58&gt;=50,"Above 50")</f>
+        <v>Above 70</v>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E59">
+        <v>55</v>
+      </c>
+      <c r="F59" t="str">
+        <f t="shared" ref="F59:F64" si="2">IF(E59&gt;=80,"Above 80",IF(E59&gt;=70,"Above 70",IF(E59&gt;=60,"Above 60",IF(E59&gt;=50,"Above 50","Under 50"))))</f>
+        <v>Above 50</v>
+      </c>
+      <c r="G59" t="str" cm="1">
+        <f t="array" ref="G59">_xlfn.IFS(E59&gt;=80,"Above 80",E59&gt;=70,"Above 70",E59&gt;=60,"Above 60",E59&gt;=50,"Above 50")</f>
+        <v>Above 50</v>
+      </c>
+      <c r="H59" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E60">
+        <v>78</v>
+      </c>
+      <c r="F60" t="str">
+        <f t="shared" si="2"/>
+        <v>Above 70</v>
+      </c>
+      <c r="G60" t="str" cm="1">
+        <f t="array" ref="G60">_xlfn.IFS(E60&gt;=80,"Above 80",E60&gt;=70,"Above 70",E60&gt;=60,"Above 60",E60&gt;=50,"Above 50")</f>
+        <v>Above 70</v>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E61">
+        <v>80</v>
+      </c>
+      <c r="F61" t="str">
+        <f t="shared" si="2"/>
+        <v>Above 80</v>
+      </c>
+      <c r="G61" t="str" cm="1">
+        <f t="array" ref="G61">_xlfn.IFS(E61&gt;=80,"Above 80",E61&gt;=70,"Above 70",E61&gt;=60,"Above 60",E61&gt;=50,"Above 50")</f>
+        <v>Above 80</v>
+      </c>
+      <c r="H61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E62">
+        <v>89</v>
+      </c>
+      <c r="F62" t="str">
+        <f t="shared" si="2"/>
+        <v>Above 80</v>
+      </c>
+      <c r="G62" t="str" cm="1">
+        <f t="array" ref="G62">_xlfn.IFS(E62&gt;=80,"Above 80",E62&gt;=70,"Above 70",E62&gt;=60,"Above 60",E62&gt;=50,"Above 50")</f>
+        <v>Above 80</v>
+      </c>
+    </row>
+    <row r="63" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E63">
+        <v>56</v>
+      </c>
+      <c r="F63" t="str">
+        <f t="shared" si="2"/>
+        <v>Above 50</v>
+      </c>
+      <c r="G63" t="str" cm="1">
+        <f t="array" ref="G63">_xlfn.IFS(E63&gt;=80,"Above 80",E63&gt;=70,"Above 70",E63&gt;=60,"Above 60",E63&gt;=50,"Above 50")</f>
+        <v>Above 50</v>
+      </c>
+    </row>
+    <row r="64" spans="5:9" x14ac:dyDescent="0.25">
+      <c r="E64">
+        <v>75</v>
+      </c>
+      <c r="F64" t="str">
+        <f t="shared" si="2"/>
+        <v>Above 70</v>
+      </c>
+      <c r="G64" t="str" cm="1">
+        <f t="array" ref="G64">_xlfn.IFS(E64&gt;=80,"Above 80",E64&gt;=70,"Above 70",E64&gt;=60,"Above 60",E64&gt;=50,"Above 50")</f>
+        <v>Above 70</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F66" t="s">
+        <v>66</v>
+      </c>
+      <c r="G66" t="s">
+        <v>67</v>
+      </c>
+      <c r="H66" t="s">
+        <v>68</v>
+      </c>
+      <c r="I66" t="s">
+        <v>69</v>
+      </c>
+      <c r="J66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D67">
+        <v>60</v>
+      </c>
+      <c r="E67">
+        <v>89</v>
+      </c>
+      <c r="F67" t="b">
+        <f>OR(D67&gt;=35,E67&gt;=35)</f>
+        <v>1</v>
+      </c>
+      <c r="G67" t="b">
+        <f>AND(D67&gt;=35,E67&gt;=35)</f>
+        <v>1</v>
+      </c>
+      <c r="H67" t="str">
+        <f>IF(F67,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="I67" t="str">
+        <f>IF(G67,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="J67" t="b">
+        <f>_xlfn.XOR(D67&gt;=35,E67&gt;=35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D68">
+        <v>55</v>
+      </c>
+      <c r="E68">
+        <v>67</v>
+      </c>
+      <c r="F68" t="b">
+        <f t="shared" ref="F68:F72" si="3">OR(D68&gt;=35,E68&gt;=35)</f>
+        <v>1</v>
+      </c>
+      <c r="G68" t="b">
+        <f t="shared" ref="G68:G72" si="4">AND(D68&gt;=35,E68&gt;=35)</f>
+        <v>1</v>
+      </c>
+      <c r="H68" t="str">
+        <f t="shared" ref="H68:H72" si="5">IF(F68,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="I68" t="str">
+        <f t="shared" ref="I68:I72" si="6">IF(G68,"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="J68" t="b">
+        <f t="shared" ref="J68:J72" si="7">_xlfn.XOR(D68&gt;=35,E68&gt;=35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D69">
+        <v>47</v>
+      </c>
+      <c r="E69">
+        <v>56</v>
+      </c>
+      <c r="F69" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G69" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H69" t="str">
+        <f t="shared" si="5"/>
+        <v>Pass</v>
+      </c>
+      <c r="I69" t="str">
+        <f t="shared" si="6"/>
+        <v>Pass</v>
+      </c>
+      <c r="J69" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D70">
+        <v>78</v>
+      </c>
+      <c r="E70">
+        <v>86</v>
+      </c>
+      <c r="F70" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G70" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H70" t="str">
+        <f t="shared" si="5"/>
+        <v>Pass</v>
+      </c>
+      <c r="I70" t="str">
+        <f t="shared" si="6"/>
+        <v>Pass</v>
+      </c>
+      <c r="J70" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D71">
+        <v>33</v>
+      </c>
+      <c r="E71">
+        <v>89</v>
+      </c>
+      <c r="F71" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G71" t="b">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H71" t="str">
+        <f t="shared" si="5"/>
+        <v>Pass</v>
+      </c>
+      <c r="I71" t="str">
+        <f t="shared" si="6"/>
+        <v>Fail</v>
+      </c>
+      <c r="J71" t="b">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D72">
+        <v>57</v>
+      </c>
+      <c r="E72">
+        <v>56</v>
+      </c>
+      <c r="F72" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="G72" t="b">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="H72" t="str">
+        <f t="shared" si="5"/>
+        <v>Pass</v>
+      </c>
+      <c r="I72" t="str">
+        <f t="shared" si="6"/>
+        <v>Pass</v>
+      </c>
+      <c r="J72" t="b">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G75" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1</v>
+      </c>
+      <c r="B76">
+        <v>100001</v>
+      </c>
+      <c r="C76" t="s">
+        <v>88</v>
+      </c>
+      <c r="D76" s="9">
+        <v>729</v>
+      </c>
+      <c r="E76" t="s">
+        <v>89</v>
+      </c>
+      <c r="F76" t="s">
+        <v>83</v>
+      </c>
+      <c r="G76" s="9">
+        <v>19</v>
+      </c>
+      <c r="H76" s="10">
+        <v>194164</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2</v>
+      </c>
+      <c r="B77">
+        <v>100002</v>
+      </c>
+      <c r="C77" t="s">
+        <v>90</v>
+      </c>
+      <c r="D77" s="9">
+        <v>744</v>
+      </c>
+      <c r="E77" t="s">
+        <v>91</v>
+      </c>
+      <c r="F77" t="s">
+        <v>85</v>
+      </c>
+      <c r="G77" s="9">
+        <v>53</v>
+      </c>
+      <c r="H77" s="10">
+        <v>195018</v>
+      </c>
+      <c r="I77" t="s">
+        <v>14</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>3</v>
+      </c>
+      <c r="B78">
+        <v>100003</v>
+      </c>
+      <c r="C78" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78" s="9">
+        <v>789</v>
+      </c>
+      <c r="E78" t="s">
+        <v>93</v>
+      </c>
+      <c r="F78" t="s">
+        <v>83</v>
+      </c>
+      <c r="G78" s="9">
+        <v>30</v>
+      </c>
+      <c r="H78" s="10">
+        <v>178650</v>
+      </c>
+      <c r="I78" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78">
+        <f>COUNT(B75:B177)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>4</v>
+      </c>
+      <c r="B79">
+        <v>100004</v>
+      </c>
+      <c r="C79" t="s">
+        <v>94</v>
+      </c>
+      <c r="D79" s="9">
+        <v>576</v>
+      </c>
+      <c r="E79" t="s">
+        <v>95</v>
+      </c>
+      <c r="F79" t="s">
+        <v>83</v>
+      </c>
+      <c r="G79" s="9">
+        <v>48</v>
+      </c>
+      <c r="H79" s="10">
+        <v>25710</v>
+      </c>
+      <c r="I79" t="s">
+        <v>113</v>
+      </c>
+      <c r="J79">
+        <f>COUNTA(B75:B179)</f>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>5</v>
+      </c>
+      <c r="B80">
+        <v>100005</v>
+      </c>
+      <c r="C80" t="s">
+        <v>96</v>
+      </c>
+      <c r="D80" s="9">
+        <v>591</v>
+      </c>
+      <c r="E80" t="s">
+        <v>89</v>
+      </c>
+      <c r="F80" t="s">
+        <v>85</v>
+      </c>
+      <c r="G80" s="9">
+        <v>28</v>
+      </c>
+      <c r="H80" s="10">
+        <v>156201</v>
+      </c>
+      <c r="I80" t="s">
+        <v>114</v>
+      </c>
+      <c r="J80">
+        <f>COUNTIFS(E76:E175,E79,F76:F175,F134)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>100006</v>
+      </c>
+      <c r="C81" t="s">
+        <v>97</v>
+      </c>
+      <c r="D81" s="9">
+        <v>692</v>
+      </c>
+      <c r="E81" t="s">
+        <v>91</v>
+      </c>
+      <c r="F81" t="s">
+        <v>83</v>
+      </c>
+      <c r="G81" s="9">
+        <v>29</v>
+      </c>
+      <c r="H81" s="10">
+        <v>213952</v>
+      </c>
+      <c r="I81" t="s">
+        <v>115</v>
+      </c>
+      <c r="J81">
+        <f>COUNTIF(E75:G175,F78)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>7</v>
+      </c>
+      <c r="B82">
+        <v>100007</v>
+      </c>
+      <c r="C82" t="s">
+        <v>98</v>
+      </c>
+      <c r="D82" s="9">
+        <v>437</v>
+      </c>
+      <c r="E82" t="s">
+        <v>93</v>
+      </c>
+      <c r="F82" t="s">
+        <v>85</v>
+      </c>
+      <c r="G82" s="9">
+        <v>58</v>
+      </c>
+      <c r="H82" s="10">
+        <v>176103</v>
+      </c>
+      <c r="I82" t="s">
+        <v>119</v>
+      </c>
+      <c r="J82">
+        <f>_xlfn.STDEV.P(G76:G175)</f>
+        <v>11.647227137821259</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>8</v>
+      </c>
+      <c r="B83">
+        <v>100008</v>
+      </c>
+      <c r="C83" t="s">
+        <v>99</v>
+      </c>
+      <c r="D83" s="9">
+        <v>416</v>
+      </c>
+      <c r="E83" t="s">
+        <v>95</v>
+      </c>
+      <c r="F83" t="s">
+        <v>83</v>
+      </c>
+      <c r="G83" s="9">
+        <v>46</v>
+      </c>
+      <c r="H83" s="10">
+        <v>57283</v>
+      </c>
+      <c r="I83" t="s">
+        <v>118</v>
+      </c>
+      <c r="J83">
+        <f>_xlfn.STDEV.S(G76:G175)</f>
+        <v>11.705903716423688</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>9</v>
+      </c>
+      <c r="B84">
+        <v>100009</v>
+      </c>
+      <c r="C84" t="s">
+        <v>100</v>
+      </c>
+      <c r="D84" s="9">
+        <v>368</v>
+      </c>
+      <c r="E84" t="s">
+        <v>89</v>
+      </c>
+      <c r="F84" t="s">
+        <v>85</v>
+      </c>
+      <c r="G84" s="9">
+        <v>18</v>
+      </c>
+      <c r="H84" s="10">
+        <v>227626</v>
+      </c>
+      <c r="I84" t="s">
+        <v>116</v>
+      </c>
+      <c r="J84" s="9">
+        <f>AVERAGE(G76:G175)</f>
+        <v>37.39</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>10</v>
+      </c>
+      <c r="B85">
+        <v>100010</v>
+      </c>
+      <c r="C85" t="s">
+        <v>101</v>
+      </c>
+      <c r="D85" s="9">
+        <v>476</v>
+      </c>
+      <c r="E85" t="s">
+        <v>91</v>
+      </c>
+      <c r="F85" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85" s="9">
+        <v>39</v>
+      </c>
+      <c r="H85" s="10">
+        <v>260233</v>
+      </c>
+      <c r="I85" t="s">
+        <v>117</v>
+      </c>
+      <c r="J85" s="9">
+        <f>MEDIAN(G76:G175)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>11</v>
+      </c>
+      <c r="B86">
+        <v>100011</v>
+      </c>
+      <c r="C86" t="s">
+        <v>102</v>
+      </c>
+      <c r="D86" s="9">
+        <v>574</v>
+      </c>
+      <c r="E86" t="s">
+        <v>93</v>
+      </c>
+      <c r="F86" t="s">
+        <v>83</v>
+      </c>
+      <c r="G86" s="9">
+        <v>30</v>
+      </c>
+      <c r="H86" s="10">
+        <v>168272</v>
+      </c>
+      <c r="I86" t="s">
+        <v>120</v>
+      </c>
+      <c r="J86">
+        <f>MODE(G76:G175)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>12</v>
+      </c>
+      <c r="B87">
+        <v>100012</v>
+      </c>
+      <c r="C87" t="s">
+        <v>103</v>
+      </c>
+      <c r="D87" s="9">
+        <v>797</v>
+      </c>
+      <c r="E87" t="s">
+        <v>95</v>
+      </c>
+      <c r="F87" t="s">
+        <v>83</v>
+      </c>
+      <c r="G87" s="9">
+        <v>27</v>
+      </c>
+      <c r="H87" s="10">
+        <v>68503</v>
+      </c>
+      <c r="I87" t="s">
+        <v>121</v>
+      </c>
+      <c r="J87">
+        <f>_xlfn.VAR.P(G76:G175)</f>
+        <v>135.65790000000001</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>13</v>
+      </c>
+      <c r="B88">
+        <v>100013</v>
+      </c>
+      <c r="C88" t="s">
+        <v>104</v>
+      </c>
+      <c r="D88" s="9">
+        <v>493</v>
+      </c>
+      <c r="E88" t="s">
+        <v>89</v>
+      </c>
+      <c r="F88" t="s">
+        <v>85</v>
+      </c>
+      <c r="G88" s="9">
+        <v>34</v>
+      </c>
+      <c r="H88" s="10">
+        <v>22604</v>
+      </c>
+      <c r="I88" t="s">
+        <v>122</v>
+      </c>
+      <c r="J88">
+        <f>_xlfn.VAR.S(G76:G175)</f>
+        <v>137.02818181818191</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>14</v>
+      </c>
+      <c r="B89">
+        <v>100014</v>
+      </c>
+      <c r="C89" t="s">
+        <v>105</v>
+      </c>
+      <c r="D89" s="9">
+        <v>803</v>
+      </c>
+      <c r="E89" t="s">
+        <v>91</v>
+      </c>
+      <c r="F89" t="s">
+        <v>85</v>
+      </c>
+      <c r="G89" s="9">
+        <v>28</v>
+      </c>
+      <c r="H89" s="10">
+        <v>164365</v>
+      </c>
+      <c r="I89" t="s">
+        <v>123</v>
+      </c>
+      <c r="J89">
+        <f>COUNTBLANK(G76:G695)</f>
+        <v>515</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>15</v>
+      </c>
+      <c r="B90">
+        <v>100015</v>
+      </c>
+      <c r="C90" t="s">
+        <v>106</v>
+      </c>
+      <c r="D90" s="9">
+        <v>442</v>
+      </c>
+      <c r="E90" t="s">
+        <v>93</v>
+      </c>
+      <c r="F90" t="s">
+        <v>83</v>
+      </c>
+      <c r="G90" s="9">
+        <v>22</v>
+      </c>
+      <c r="H90" s="10">
+        <v>180396</v>
+      </c>
+      <c r="I90" t="s">
+        <v>124</v>
+      </c>
+      <c r="J90">
+        <f>CORREL(D76:D175,G76:G175)</f>
+        <v>-8.3913334776442056E-2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>16</v>
+      </c>
+      <c r="B91">
+        <v>100016</v>
+      </c>
+      <c r="C91" t="s">
+        <v>107</v>
+      </c>
+      <c r="D91" s="9">
+        <v>407</v>
+      </c>
+      <c r="E91" t="s">
+        <v>95</v>
+      </c>
+      <c r="F91" t="s">
+        <v>83</v>
+      </c>
+      <c r="G91" s="9">
+        <v>42</v>
+      </c>
+      <c r="H91" s="10">
+        <v>13669</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>17</v>
+      </c>
+      <c r="B92">
+        <v>100017</v>
+      </c>
+      <c r="C92" t="s">
+        <v>108</v>
+      </c>
+      <c r="D92" s="9">
+        <v>472</v>
+      </c>
+      <c r="E92" t="s">
+        <v>89</v>
+      </c>
+      <c r="F92" t="s">
+        <v>83</v>
+      </c>
+      <c r="G92" s="9">
+        <v>51</v>
+      </c>
+      <c r="H92" s="10">
+        <v>18758</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>18</v>
+      </c>
+      <c r="B93">
+        <v>100018</v>
+      </c>
+      <c r="C93" t="s">
+        <v>109</v>
+      </c>
+      <c r="D93" s="9">
+        <v>833</v>
+      </c>
+      <c r="E93" t="s">
+        <v>91</v>
+      </c>
+      <c r="F93" t="s">
+        <v>83</v>
+      </c>
+      <c r="G93" s="9">
+        <v>34</v>
+      </c>
+      <c r="H93" s="10">
+        <v>129221</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>19</v>
+      </c>
+      <c r="B94">
+        <v>100019</v>
+      </c>
+      <c r="C94" t="s">
+        <v>110</v>
+      </c>
+      <c r="D94" s="9">
+        <v>659</v>
+      </c>
+      <c r="E94" t="s">
+        <v>93</v>
+      </c>
+      <c r="F94" t="s">
+        <v>85</v>
+      </c>
+      <c r="G94" s="9">
+        <v>19</v>
+      </c>
+      <c r="H94" s="10">
+        <v>217058</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>20</v>
+      </c>
+      <c r="B95">
+        <v>100020</v>
+      </c>
+      <c r="C95" t="s">
+        <v>111</v>
+      </c>
+      <c r="D95" s="9">
+        <v>522</v>
+      </c>
+      <c r="E95" t="s">
+        <v>95</v>
+      </c>
+      <c r="F95" t="s">
+        <v>85</v>
+      </c>
+      <c r="G95" s="9">
+        <v>23</v>
+      </c>
+      <c r="H95" s="10">
+        <v>50584</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>21</v>
+      </c>
+      <c r="B96">
+        <v>100021</v>
+      </c>
+      <c r="C96" t="s">
+        <v>88</v>
+      </c>
+      <c r="D96" s="9">
+        <v>674</v>
+      </c>
+      <c r="E96" t="s">
+        <v>89</v>
+      </c>
+      <c r="F96" t="s">
+        <v>85</v>
+      </c>
+      <c r="G96" s="9">
+        <v>24</v>
+      </c>
+      <c r="H96" s="10">
+        <v>171441</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>22</v>
+      </c>
+      <c r="B97">
+        <v>100022</v>
+      </c>
+      <c r="C97" t="s">
+        <v>90</v>
+      </c>
+      <c r="D97" s="9">
+        <v>637</v>
+      </c>
+      <c r="E97" t="s">
+        <v>91</v>
+      </c>
+      <c r="F97" t="s">
+        <v>83</v>
+      </c>
+      <c r="G97" s="9">
+        <v>57</v>
+      </c>
+      <c r="H97" s="10">
+        <v>62722</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>23</v>
+      </c>
+      <c r="B98">
+        <v>100023</v>
+      </c>
+      <c r="C98" t="s">
+        <v>92</v>
+      </c>
+      <c r="D98" s="9">
+        <v>527</v>
+      </c>
+      <c r="E98" t="s">
+        <v>93</v>
+      </c>
+      <c r="F98" t="s">
+        <v>83</v>
+      </c>
+      <c r="G98" s="9">
+        <v>53</v>
+      </c>
+      <c r="H98" s="10">
+        <v>119346</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>24</v>
+      </c>
+      <c r="B99">
+        <v>100024</v>
+      </c>
+      <c r="C99" t="s">
+        <v>94</v>
+      </c>
+      <c r="D99" s="9">
+        <v>406</v>
+      </c>
+      <c r="E99" t="s">
+        <v>95</v>
+      </c>
+      <c r="F99" t="s">
+        <v>83</v>
+      </c>
+      <c r="G99" s="9">
+        <v>19</v>
+      </c>
+      <c r="H99" s="10">
+        <v>112944</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>25</v>
+      </c>
+      <c r="B100">
+        <v>100025</v>
+      </c>
+      <c r="C100" t="s">
+        <v>96</v>
+      </c>
+      <c r="D100" s="9">
+        <v>648</v>
+      </c>
+      <c r="E100" t="s">
+        <v>89</v>
+      </c>
+      <c r="F100" t="s">
+        <v>83</v>
+      </c>
+      <c r="G100" s="9">
+        <v>56</v>
+      </c>
+      <c r="H100" s="10">
+        <v>172469</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>26</v>
+      </c>
+      <c r="B101">
+        <v>100026</v>
+      </c>
+      <c r="C101" t="s">
+        <v>97</v>
+      </c>
+      <c r="D101" s="9">
+        <v>820</v>
+      </c>
+      <c r="E101" t="s">
+        <v>91</v>
+      </c>
+      <c r="F101" t="s">
+        <v>85</v>
+      </c>
+      <c r="G101" s="9">
+        <v>18</v>
+      </c>
+      <c r="H101" s="10">
+        <v>272655</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>27</v>
+      </c>
+      <c r="B102">
+        <v>100027</v>
+      </c>
+      <c r="C102" t="s">
+        <v>98</v>
+      </c>
+      <c r="D102" s="9">
+        <v>693</v>
+      </c>
+      <c r="E102" t="s">
+        <v>93</v>
+      </c>
+      <c r="F102" t="s">
+        <v>83</v>
+      </c>
+      <c r="G102" s="9">
+        <v>39</v>
+      </c>
+      <c r="H102" s="10">
+        <v>146244</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>28</v>
+      </c>
+      <c r="B103">
+        <v>100028</v>
+      </c>
+      <c r="C103" t="s">
+        <v>99</v>
+      </c>
+      <c r="D103" s="9">
+        <v>548</v>
+      </c>
+      <c r="E103" t="s">
+        <v>95</v>
+      </c>
+      <c r="F103" t="s">
+        <v>85</v>
+      </c>
+      <c r="G103" s="9">
+        <v>54</v>
+      </c>
+      <c r="H103" s="10">
+        <v>241615</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>29</v>
+      </c>
+      <c r="B104">
+        <v>100029</v>
+      </c>
+      <c r="C104" t="s">
+        <v>100</v>
+      </c>
+      <c r="D104" s="9">
+        <v>576</v>
+      </c>
+      <c r="E104" t="s">
+        <v>89</v>
+      </c>
+      <c r="F104" t="s">
+        <v>85</v>
+      </c>
+      <c r="G104" s="9">
+        <v>28</v>
+      </c>
+      <c r="H104" s="10">
+        <v>151072</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>30</v>
+      </c>
+      <c r="B105">
+        <v>100030</v>
+      </c>
+      <c r="C105" t="s">
+        <v>101</v>
+      </c>
+      <c r="D105" s="9">
+        <v>468</v>
+      </c>
+      <c r="E105" t="s">
+        <v>91</v>
+      </c>
+      <c r="F105" t="s">
+        <v>85</v>
+      </c>
+      <c r="G105" s="9">
+        <v>29</v>
+      </c>
+      <c r="H105" s="10">
+        <v>135620</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>31</v>
+      </c>
+      <c r="B106">
+        <v>100031</v>
+      </c>
+      <c r="C106" t="s">
+        <v>102</v>
+      </c>
+      <c r="D106" s="9">
+        <v>790</v>
+      </c>
+      <c r="E106" t="s">
+        <v>93</v>
+      </c>
+      <c r="F106" t="s">
+        <v>83</v>
+      </c>
+      <c r="G106" s="9">
+        <v>44</v>
+      </c>
+      <c r="H106" s="10">
+        <v>220516</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>32</v>
+      </c>
+      <c r="B107">
+        <v>100032</v>
+      </c>
+      <c r="C107" t="s">
+        <v>103</v>
+      </c>
+      <c r="D107" s="9">
+        <v>476</v>
+      </c>
+      <c r="E107" t="s">
+        <v>95</v>
+      </c>
+      <c r="F107" t="s">
+        <v>85</v>
+      </c>
+      <c r="G107" s="9">
+        <v>41</v>
+      </c>
+      <c r="H107" s="10">
+        <v>191371</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>33</v>
+      </c>
+      <c r="B108">
+        <v>100033</v>
+      </c>
+      <c r="C108" t="s">
+        <v>104</v>
+      </c>
+      <c r="D108" s="9">
+        <v>836</v>
+      </c>
+      <c r="E108" t="s">
+        <v>89</v>
+      </c>
+      <c r="F108" t="s">
+        <v>85</v>
+      </c>
+      <c r="G108" s="9">
+        <v>33</v>
+      </c>
+      <c r="H108" s="10">
+        <v>143934</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>34</v>
+      </c>
+      <c r="B109">
+        <v>100034</v>
+      </c>
+      <c r="C109" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" s="9">
+        <v>597</v>
+      </c>
+      <c r="E109" t="s">
+        <v>91</v>
+      </c>
+      <c r="F109" t="s">
+        <v>83</v>
+      </c>
+      <c r="G109" s="9">
+        <v>50</v>
+      </c>
+      <c r="H109" s="10">
+        <v>266091</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>35</v>
+      </c>
+      <c r="B110">
+        <v>100035</v>
+      </c>
+      <c r="C110" t="s">
+        <v>106</v>
+      </c>
+      <c r="D110" s="9">
+        <v>677</v>
+      </c>
+      <c r="E110" t="s">
+        <v>93</v>
+      </c>
+      <c r="F110" t="s">
+        <v>85</v>
+      </c>
+      <c r="G110" s="9">
+        <v>37</v>
+      </c>
+      <c r="H110" s="10">
+        <v>73963</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>36</v>
+      </c>
+      <c r="B111">
+        <v>100036</v>
+      </c>
+      <c r="C111" t="s">
+        <v>107</v>
+      </c>
+      <c r="D111" s="9">
+        <v>587</v>
+      </c>
+      <c r="E111" t="s">
+        <v>95</v>
+      </c>
+      <c r="F111" t="s">
+        <v>83</v>
+      </c>
+      <c r="G111" s="9">
+        <v>32</v>
+      </c>
+      <c r="H111" s="10">
+        <v>194354</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>37</v>
+      </c>
+      <c r="B112">
+        <v>100037</v>
+      </c>
+      <c r="C112" t="s">
+        <v>108</v>
+      </c>
+      <c r="D112" s="9">
+        <v>456</v>
+      </c>
+      <c r="E112" t="s">
+        <v>89</v>
+      </c>
+      <c r="F112" t="s">
+        <v>83</v>
+      </c>
+      <c r="G112" s="9">
+        <v>33</v>
+      </c>
+      <c r="H112" s="10">
+        <v>149193</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>38</v>
+      </c>
+      <c r="B113">
+        <v>100038</v>
+      </c>
+      <c r="C113" t="s">
+        <v>109</v>
+      </c>
+      <c r="D113" s="9">
+        <v>846</v>
+      </c>
+      <c r="E113" t="s">
+        <v>91</v>
+      </c>
+      <c r="F113" t="s">
+        <v>85</v>
+      </c>
+      <c r="G113" s="9">
+        <v>59</v>
+      </c>
+      <c r="H113" s="10">
+        <v>232997</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>39</v>
+      </c>
+      <c r="B114">
+        <v>100039</v>
+      </c>
+      <c r="C114" t="s">
+        <v>110</v>
+      </c>
+      <c r="D114" s="9">
+        <v>623</v>
+      </c>
+      <c r="E114" t="s">
+        <v>93</v>
+      </c>
+      <c r="F114" t="s">
+        <v>83</v>
+      </c>
+      <c r="G114" s="9">
+        <v>46</v>
+      </c>
+      <c r="H114" s="10">
+        <v>57885</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>40</v>
+      </c>
+      <c r="B115">
+        <v>100040</v>
+      </c>
+      <c r="C115" t="s">
+        <v>111</v>
+      </c>
+      <c r="D115" s="9">
+        <v>364</v>
+      </c>
+      <c r="E115" t="s">
+        <v>95</v>
+      </c>
+      <c r="F115" t="s">
+        <v>83</v>
+      </c>
+      <c r="G115" s="9">
+        <v>35</v>
+      </c>
+      <c r="H115" s="10">
+        <v>201142</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>41</v>
+      </c>
+      <c r="B116">
+        <v>100041</v>
+      </c>
+      <c r="C116" t="s">
+        <v>88</v>
+      </c>
+      <c r="D116" s="9">
+        <v>362</v>
+      </c>
+      <c r="E116" t="s">
+        <v>89</v>
+      </c>
+      <c r="F116" t="s">
+        <v>85</v>
+      </c>
+      <c r="G116" s="9">
+        <v>55</v>
+      </c>
+      <c r="H116" s="10">
+        <v>198938</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>42</v>
+      </c>
+      <c r="B117">
+        <v>100042</v>
+      </c>
+      <c r="C117" t="s">
+        <v>90</v>
+      </c>
+      <c r="D117" s="9">
+        <v>443</v>
+      </c>
+      <c r="E117" t="s">
+        <v>91</v>
+      </c>
+      <c r="F117" t="s">
+        <v>85</v>
+      </c>
+      <c r="G117" s="9">
+        <v>42</v>
+      </c>
+      <c r="H117" s="10">
+        <v>160456</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>43</v>
+      </c>
+      <c r="B118">
+        <v>100043</v>
+      </c>
+      <c r="C118" t="s">
+        <v>92</v>
+      </c>
+      <c r="D118" s="9">
+        <v>578</v>
+      </c>
+      <c r="E118" t="s">
+        <v>93</v>
+      </c>
+      <c r="F118" t="s">
+        <v>83</v>
+      </c>
+      <c r="G118" s="9">
+        <v>27</v>
+      </c>
+      <c r="H118" s="10">
+        <v>105437</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>44</v>
+      </c>
+      <c r="B119">
+        <v>100044</v>
+      </c>
+      <c r="C119" t="s">
+        <v>94</v>
+      </c>
+      <c r="D119" s="9">
+        <v>844</v>
+      </c>
+      <c r="E119" t="s">
+        <v>95</v>
+      </c>
+      <c r="F119" t="s">
+        <v>85</v>
+      </c>
+      <c r="G119" s="9">
+        <v>29</v>
+      </c>
+      <c r="H119" s="10">
+        <v>128955</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>45</v>
+      </c>
+      <c r="B120">
+        <v>100045</v>
+      </c>
+      <c r="C120" t="s">
+        <v>96</v>
+      </c>
+      <c r="D120" s="9">
+        <v>376</v>
+      </c>
+      <c r="E120" t="s">
+        <v>89</v>
+      </c>
+      <c r="F120" t="s">
+        <v>85</v>
+      </c>
+      <c r="G120" s="9">
+        <v>37</v>
+      </c>
+      <c r="H120" s="10">
+        <v>246198</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>46</v>
+      </c>
+      <c r="B121">
+        <v>100046</v>
+      </c>
+      <c r="C121" t="s">
+        <v>97</v>
+      </c>
+      <c r="D121" s="9">
+        <v>529</v>
+      </c>
+      <c r="E121" t="s">
+        <v>91</v>
+      </c>
+      <c r="F121" t="s">
+        <v>83</v>
+      </c>
+      <c r="G121" s="9">
+        <v>45</v>
+      </c>
+      <c r="H121" s="10">
+        <v>216027</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>47</v>
+      </c>
+      <c r="B122">
+        <v>100047</v>
+      </c>
+      <c r="C122" t="s">
+        <v>98</v>
+      </c>
+      <c r="D122" s="9">
+        <v>783</v>
+      </c>
+      <c r="E122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F122" t="s">
+        <v>85</v>
+      </c>
+      <c r="G122" s="9">
+        <v>18</v>
+      </c>
+      <c r="H122" s="10">
+        <v>76209</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>48</v>
+      </c>
+      <c r="B123">
+        <v>100048</v>
+      </c>
+      <c r="C123" t="s">
+        <v>99</v>
+      </c>
+      <c r="D123" s="9">
+        <v>576</v>
+      </c>
+      <c r="E123" t="s">
+        <v>95</v>
+      </c>
+      <c r="F123" t="s">
+        <v>85</v>
+      </c>
+      <c r="G123" s="9">
+        <v>60</v>
+      </c>
+      <c r="H123" s="10">
+        <v>139439</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>49</v>
+      </c>
+      <c r="B124">
+        <v>100049</v>
+      </c>
+      <c r="C124" t="s">
+        <v>100</v>
+      </c>
+      <c r="D124" s="9">
+        <v>787</v>
+      </c>
+      <c r="E124" t="s">
+        <v>89</v>
+      </c>
+      <c r="F124" t="s">
+        <v>83</v>
+      </c>
+      <c r="G124" s="9">
+        <v>36</v>
+      </c>
+      <c r="H124" s="10">
+        <v>183558</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>50</v>
+      </c>
+      <c r="B125">
+        <v>100050</v>
+      </c>
+      <c r="C125" t="s">
+        <v>101</v>
+      </c>
+      <c r="D125" s="9">
+        <v>710</v>
+      </c>
+      <c r="E125" t="s">
+        <v>91</v>
+      </c>
+      <c r="F125" t="s">
+        <v>83</v>
+      </c>
+      <c r="G125" s="9">
+        <v>30</v>
+      </c>
+      <c r="H125" s="10">
+        <v>175746</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>51</v>
+      </c>
+      <c r="B126">
+        <v>100051</v>
+      </c>
+      <c r="C126" t="s">
+        <v>102</v>
+      </c>
+      <c r="D126" s="9">
+        <v>392</v>
+      </c>
+      <c r="E126" t="s">
+        <v>93</v>
+      </c>
+      <c r="F126" t="s">
+        <v>83</v>
+      </c>
+      <c r="G126" s="9">
+        <v>23</v>
+      </c>
+      <c r="H126" s="10">
+        <v>14943</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>52</v>
+      </c>
+      <c r="B127">
+        <v>100052</v>
+      </c>
+      <c r="C127" t="s">
+        <v>103</v>
+      </c>
+      <c r="D127" s="9">
+        <v>549</v>
+      </c>
+      <c r="E127" t="s">
+        <v>95</v>
+      </c>
+      <c r="F127" t="s">
+        <v>83</v>
+      </c>
+      <c r="G127" s="9">
+        <v>25</v>
+      </c>
+      <c r="H127" s="10">
+        <v>53241</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>53</v>
+      </c>
+      <c r="B128">
+        <v>100053</v>
+      </c>
+      <c r="C128" t="s">
+        <v>104</v>
+      </c>
+      <c r="D128" s="9">
+        <v>401</v>
+      </c>
+      <c r="E128" t="s">
+        <v>89</v>
+      </c>
+      <c r="F128" t="s">
+        <v>83</v>
+      </c>
+      <c r="G128" s="9">
+        <v>43</v>
+      </c>
+      <c r="H128" s="10">
+        <v>156572</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>54</v>
+      </c>
+      <c r="B129">
+        <v>100054</v>
+      </c>
+      <c r="C129" t="s">
+        <v>105</v>
+      </c>
+      <c r="D129" s="9">
+        <v>620</v>
+      </c>
+      <c r="E129" t="s">
+        <v>91</v>
+      </c>
+      <c r="F129" t="s">
+        <v>83</v>
+      </c>
+      <c r="G129" s="9">
+        <v>25</v>
+      </c>
+      <c r="H129" s="10">
+        <v>191609</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>55</v>
+      </c>
+      <c r="B130">
+        <v>100055</v>
+      </c>
+      <c r="C130" t="s">
+        <v>106</v>
+      </c>
+      <c r="D130" s="9">
+        <v>423</v>
+      </c>
+      <c r="E130" t="s">
+        <v>93</v>
+      </c>
+      <c r="F130" t="s">
+        <v>85</v>
+      </c>
+      <c r="G130" s="9">
+        <v>29</v>
+      </c>
+      <c r="H130" s="10">
+        <v>25440</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>56</v>
+      </c>
+      <c r="B131">
+        <v>100056</v>
+      </c>
+      <c r="C131" t="s">
+        <v>107</v>
+      </c>
+      <c r="D131" s="9">
+        <v>803</v>
+      </c>
+      <c r="E131" t="s">
+        <v>95</v>
+      </c>
+      <c r="F131" t="s">
+        <v>83</v>
+      </c>
+      <c r="G131" s="9">
+        <v>30</v>
+      </c>
+      <c r="H131" s="10">
+        <v>66194</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>57</v>
+      </c>
+      <c r="B132">
+        <v>100057</v>
+      </c>
+      <c r="C132" t="s">
+        <v>108</v>
+      </c>
+      <c r="D132" s="9">
+        <v>708</v>
+      </c>
+      <c r="E132" t="s">
+        <v>89</v>
+      </c>
+      <c r="F132" t="s">
+        <v>85</v>
+      </c>
+      <c r="G132" s="9">
+        <v>20</v>
+      </c>
+      <c r="H132" s="10">
+        <v>72447</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>58</v>
+      </c>
+      <c r="B133">
+        <v>100058</v>
+      </c>
+      <c r="C133" t="s">
+        <v>109</v>
+      </c>
+      <c r="D133" s="9">
+        <v>578</v>
+      </c>
+      <c r="E133" t="s">
+        <v>91</v>
+      </c>
+      <c r="F133" t="s">
+        <v>83</v>
+      </c>
+      <c r="G133" s="9">
+        <v>47</v>
+      </c>
+      <c r="H133" s="10">
+        <v>195834</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>59</v>
+      </c>
+      <c r="B134">
+        <v>100059</v>
+      </c>
+      <c r="C134" t="s">
+        <v>110</v>
+      </c>
+      <c r="D134" s="9">
+        <v>440</v>
+      </c>
+      <c r="E134" t="s">
+        <v>93</v>
+      </c>
+      <c r="F134" t="s">
+        <v>85</v>
+      </c>
+      <c r="G134" s="9">
+        <v>43</v>
+      </c>
+      <c r="H134" s="10">
+        <v>185910</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>60</v>
+      </c>
+      <c r="B135">
+        <v>100060</v>
+      </c>
+      <c r="C135" t="s">
+        <v>111</v>
+      </c>
+      <c r="D135" s="9">
+        <v>571</v>
+      </c>
+      <c r="E135" t="s">
+        <v>95</v>
+      </c>
+      <c r="F135" t="s">
+        <v>83</v>
+      </c>
+      <c r="G135" s="9">
+        <v>42</v>
+      </c>
+      <c r="H135" s="10">
+        <v>237779</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>61</v>
+      </c>
+      <c r="B136">
+        <v>100061</v>
+      </c>
+      <c r="C136" t="s">
+        <v>88</v>
+      </c>
+      <c r="D136" s="9">
+        <v>830</v>
+      </c>
+      <c r="E136" t="s">
+        <v>89</v>
+      </c>
+      <c r="F136" t="s">
+        <v>85</v>
+      </c>
+      <c r="G136" s="9">
+        <v>57</v>
+      </c>
+      <c r="H136" s="10">
+        <v>187568</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>62</v>
+      </c>
+      <c r="B137">
+        <v>100062</v>
+      </c>
+      <c r="C137" t="s">
+        <v>90</v>
+      </c>
+      <c r="D137" s="9">
+        <v>788</v>
+      </c>
+      <c r="E137" t="s">
+        <v>91</v>
+      </c>
+      <c r="F137" t="s">
+        <v>85</v>
+      </c>
+      <c r="G137" s="9">
+        <v>22</v>
+      </c>
+      <c r="H137" s="10">
+        <v>257156</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>63</v>
+      </c>
+      <c r="B138">
+        <v>100063</v>
+      </c>
+      <c r="C138" t="s">
+        <v>92</v>
+      </c>
+      <c r="D138" s="9">
+        <v>516</v>
+      </c>
+      <c r="E138" t="s">
+        <v>93</v>
+      </c>
+      <c r="F138" t="s">
+        <v>83</v>
+      </c>
+      <c r="G138" s="9">
+        <v>30</v>
+      </c>
+      <c r="H138" s="10">
+        <v>68963</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>64</v>
+      </c>
+      <c r="B139">
+        <v>100064</v>
+      </c>
+      <c r="C139" t="s">
+        <v>94</v>
+      </c>
+      <c r="D139" s="9">
+        <v>573</v>
+      </c>
+      <c r="E139" t="s">
+        <v>95</v>
+      </c>
+      <c r="F139" t="s">
+        <v>85</v>
+      </c>
+      <c r="G139" s="9">
+        <v>47</v>
+      </c>
+      <c r="H139" s="10">
+        <v>157806</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>65</v>
+      </c>
+      <c r="B140">
+        <v>100065</v>
+      </c>
+      <c r="C140" t="s">
+        <v>96</v>
+      </c>
+      <c r="D140" s="9">
+        <v>669</v>
+      </c>
+      <c r="E140" t="s">
+        <v>89</v>
+      </c>
+      <c r="F140" t="s">
+        <v>85</v>
+      </c>
+      <c r="G140" s="9">
+        <v>38</v>
+      </c>
+      <c r="H140" s="10">
+        <v>166014</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>66</v>
+      </c>
+      <c r="B141">
+        <v>100066</v>
+      </c>
+      <c r="C141" t="s">
+        <v>97</v>
+      </c>
+      <c r="D141" s="9">
+        <v>442</v>
+      </c>
+      <c r="E141" t="s">
+        <v>91</v>
+      </c>
+      <c r="F141" t="s">
+        <v>83</v>
+      </c>
+      <c r="G141" s="9">
+        <v>41</v>
+      </c>
+      <c r="H141" s="10">
+        <v>24054</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>67</v>
+      </c>
+      <c r="B142">
+        <v>100067</v>
+      </c>
+      <c r="C142" t="s">
+        <v>98</v>
+      </c>
+      <c r="D142" s="9">
+        <v>515</v>
+      </c>
+      <c r="E142" t="s">
+        <v>93</v>
+      </c>
+      <c r="F142" t="s">
+        <v>83</v>
+      </c>
+      <c r="G142" s="9">
+        <v>31</v>
+      </c>
+      <c r="H142" s="10">
+        <v>152853</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>68</v>
+      </c>
+      <c r="B143">
+        <v>100068</v>
+      </c>
+      <c r="C143" t="s">
+        <v>99</v>
+      </c>
+      <c r="D143" s="9">
+        <v>404</v>
+      </c>
+      <c r="E143" t="s">
+        <v>95</v>
+      </c>
+      <c r="F143" t="s">
+        <v>83</v>
+      </c>
+      <c r="G143" s="9">
+        <v>19</v>
+      </c>
+      <c r="H143" s="10">
+        <v>189931</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>69</v>
+      </c>
+      <c r="B144">
+        <v>100069</v>
+      </c>
+      <c r="C144" t="s">
+        <v>100</v>
+      </c>
+      <c r="D144" s="9">
+        <v>371</v>
+      </c>
+      <c r="E144" t="s">
+        <v>89</v>
+      </c>
+      <c r="F144" t="s">
+        <v>85</v>
+      </c>
+      <c r="G144" s="9">
+        <v>38</v>
+      </c>
+      <c r="H144" s="10">
+        <v>220173</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>70</v>
+      </c>
+      <c r="B145">
+        <v>100070</v>
+      </c>
+      <c r="C145" t="s">
+        <v>101</v>
+      </c>
+      <c r="D145" s="9">
+        <v>686</v>
+      </c>
+      <c r="E145" t="s">
+        <v>91</v>
+      </c>
+      <c r="F145" t="s">
+        <v>83</v>
+      </c>
+      <c r="G145" s="9">
+        <v>47</v>
+      </c>
+      <c r="H145" s="10">
+        <v>147823</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>71</v>
+      </c>
+      <c r="B146">
+        <v>100071</v>
+      </c>
+      <c r="C146" t="s">
+        <v>102</v>
+      </c>
+      <c r="D146" s="9">
+        <v>699</v>
+      </c>
+      <c r="E146" t="s">
+        <v>93</v>
+      </c>
+      <c r="F146" t="s">
+        <v>83</v>
+      </c>
+      <c r="G146" s="9">
+        <v>47</v>
+      </c>
+      <c r="H146" s="10">
+        <v>34827</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>72</v>
+      </c>
+      <c r="B147">
+        <v>100072</v>
+      </c>
+      <c r="C147" t="s">
+        <v>103</v>
+      </c>
+      <c r="D147" s="9">
+        <v>429</v>
+      </c>
+      <c r="E147" t="s">
+        <v>95</v>
+      </c>
+      <c r="F147" t="s">
+        <v>85</v>
+      </c>
+      <c r="G147" s="9">
+        <v>23</v>
+      </c>
+      <c r="H147" s="10">
+        <v>126267</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>73</v>
+      </c>
+      <c r="B148">
+        <v>100073</v>
+      </c>
+      <c r="C148" t="s">
+        <v>104</v>
+      </c>
+      <c r="D148" s="9">
+        <v>582</v>
+      </c>
+      <c r="E148" t="s">
+        <v>89</v>
+      </c>
+      <c r="F148" t="s">
+        <v>85</v>
+      </c>
+      <c r="G148" s="9">
+        <v>42</v>
+      </c>
+      <c r="H148" s="10">
+        <v>217038</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>74</v>
+      </c>
+      <c r="B149">
+        <v>100074</v>
+      </c>
+      <c r="C149" t="s">
+        <v>105</v>
+      </c>
+      <c r="D149" s="9">
+        <v>525</v>
+      </c>
+      <c r="E149" t="s">
+        <v>91</v>
+      </c>
+      <c r="F149" t="s">
+        <v>85</v>
+      </c>
+      <c r="G149" s="9">
+        <v>50</v>
+      </c>
+      <c r="H149" s="10">
+        <v>49390</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>75</v>
+      </c>
+      <c r="B150">
+        <v>100075</v>
+      </c>
+      <c r="C150" t="s">
+        <v>106</v>
+      </c>
+      <c r="D150" s="9">
+        <v>562</v>
+      </c>
+      <c r="E150" t="s">
+        <v>93</v>
+      </c>
+      <c r="F150" t="s">
+        <v>83</v>
+      </c>
+      <c r="G150" s="9">
+        <v>44</v>
+      </c>
+      <c r="H150" s="10">
+        <v>29342</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>76</v>
+      </c>
+      <c r="B151">
+        <v>100076</v>
+      </c>
+      <c r="C151" t="s">
+        <v>107</v>
+      </c>
+      <c r="D151" s="9">
+        <v>459</v>
+      </c>
+      <c r="E151" t="s">
+        <v>95</v>
+      </c>
+      <c r="F151" t="s">
+        <v>83</v>
+      </c>
+      <c r="G151" s="9">
+        <v>51</v>
+      </c>
+      <c r="H151" s="10">
+        <v>185338</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>77</v>
+      </c>
+      <c r="B152">
+        <v>100077</v>
+      </c>
+      <c r="C152" t="s">
+        <v>108</v>
+      </c>
+      <c r="D152" s="9">
+        <v>485</v>
+      </c>
+      <c r="E152" t="s">
+        <v>89</v>
+      </c>
+      <c r="F152" t="s">
+        <v>83</v>
+      </c>
+      <c r="G152" s="9">
+        <v>56</v>
+      </c>
+      <c r="H152" s="10">
+        <v>240884</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>78</v>
+      </c>
+      <c r="B153">
+        <v>100078</v>
+      </c>
+      <c r="C153" t="s">
+        <v>109</v>
+      </c>
+      <c r="D153" s="9">
+        <v>400</v>
+      </c>
+      <c r="E153" t="s">
+        <v>91</v>
+      </c>
+      <c r="F153" t="s">
+        <v>83</v>
+      </c>
+      <c r="G153" s="9">
+        <v>47</v>
+      </c>
+      <c r="H153" s="10">
+        <v>28270</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>79</v>
+      </c>
+      <c r="B154">
+        <v>100079</v>
+      </c>
+      <c r="C154" t="s">
+        <v>110</v>
+      </c>
+      <c r="D154" s="9">
+        <v>385</v>
+      </c>
+      <c r="E154" t="s">
+        <v>93</v>
+      </c>
+      <c r="F154" t="s">
+        <v>83</v>
+      </c>
+      <c r="G154" s="9">
+        <v>50</v>
+      </c>
+      <c r="H154" s="10">
+        <v>28870</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>80</v>
+      </c>
+      <c r="B155">
+        <v>100080</v>
+      </c>
+      <c r="C155" t="s">
+        <v>111</v>
+      </c>
+      <c r="D155" s="9">
+        <v>753</v>
+      </c>
+      <c r="E155" t="s">
+        <v>95</v>
+      </c>
+      <c r="F155" t="s">
+        <v>83</v>
+      </c>
+      <c r="G155" s="9">
+        <v>58</v>
+      </c>
+      <c r="H155" s="10">
+        <v>100930</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>81</v>
+      </c>
+      <c r="B156">
+        <v>100081</v>
+      </c>
+      <c r="C156" t="s">
+        <v>88</v>
+      </c>
+      <c r="D156" s="9">
+        <v>579</v>
+      </c>
+      <c r="E156" t="s">
+        <v>89</v>
+      </c>
+      <c r="F156" t="s">
+        <v>85</v>
+      </c>
+      <c r="G156" s="9">
+        <v>36</v>
+      </c>
+      <c r="H156" s="10">
+        <v>24242</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>82</v>
+      </c>
+      <c r="B157">
+        <v>100082</v>
+      </c>
+      <c r="C157" t="s">
+        <v>90</v>
+      </c>
+      <c r="D157" s="9">
+        <v>623</v>
+      </c>
+      <c r="E157" t="s">
+        <v>91</v>
+      </c>
+      <c r="F157" t="s">
+        <v>85</v>
+      </c>
+      <c r="G157" s="9">
+        <v>26</v>
+      </c>
+      <c r="H157" s="10">
+        <v>176598</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>83</v>
+      </c>
+      <c r="B158">
+        <v>100083</v>
+      </c>
+      <c r="C158" t="s">
+        <v>92</v>
+      </c>
+      <c r="D158" s="9">
+        <v>547</v>
+      </c>
+      <c r="E158" t="s">
+        <v>93</v>
+      </c>
+      <c r="F158" t="s">
+        <v>83</v>
+      </c>
+      <c r="G158" s="9">
+        <v>48</v>
+      </c>
+      <c r="H158" s="10">
+        <v>190550</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>84</v>
+      </c>
+      <c r="B159">
+        <v>100084</v>
+      </c>
+      <c r="C159" t="s">
+        <v>94</v>
+      </c>
+      <c r="D159" s="9">
+        <v>791</v>
+      </c>
+      <c r="E159" t="s">
+        <v>95</v>
+      </c>
+      <c r="F159" t="s">
+        <v>83</v>
+      </c>
+      <c r="G159" s="9">
+        <v>35</v>
+      </c>
+      <c r="H159" s="10">
+        <v>189651</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>85</v>
+      </c>
+      <c r="B160">
+        <v>100085</v>
+      </c>
+      <c r="C160" t="s">
+        <v>96</v>
+      </c>
+      <c r="D160" s="9">
+        <v>801</v>
+      </c>
+      <c r="E160" t="s">
+        <v>89</v>
+      </c>
+      <c r="F160" t="s">
+        <v>83</v>
+      </c>
+      <c r="G160" s="9">
+        <v>46</v>
+      </c>
+      <c r="H160" s="10">
+        <v>207146</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>86</v>
+      </c>
+      <c r="B161">
+        <v>100086</v>
+      </c>
+      <c r="C161" t="s">
+        <v>97</v>
+      </c>
+      <c r="D161" s="9">
+        <v>619</v>
+      </c>
+      <c r="E161" t="s">
+        <v>91</v>
+      </c>
+      <c r="F161" t="s">
+        <v>83</v>
+      </c>
+      <c r="G161" s="9">
+        <v>31</v>
+      </c>
+      <c r="H161" s="10">
+        <v>45891</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>87</v>
+      </c>
+      <c r="B162">
+        <v>100087</v>
+      </c>
+      <c r="C162" t="s">
+        <v>98</v>
+      </c>
+      <c r="D162" s="9">
+        <v>810</v>
+      </c>
+      <c r="E162" t="s">
+        <v>93</v>
+      </c>
+      <c r="F162" t="s">
+        <v>83</v>
+      </c>
+      <c r="G162" s="9">
+        <v>37</v>
+      </c>
+      <c r="H162" s="10">
+        <v>127283</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>88</v>
+      </c>
+      <c r="B163">
+        <v>100088</v>
+      </c>
+      <c r="C163" t="s">
+        <v>99</v>
+      </c>
+      <c r="D163" s="9">
+        <v>376</v>
+      </c>
+      <c r="E163" t="s">
+        <v>95</v>
+      </c>
+      <c r="F163" t="s">
+        <v>83</v>
+      </c>
+      <c r="G163" s="9">
+        <v>21</v>
+      </c>
+      <c r="H163" s="10">
+        <v>12983</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>89</v>
+      </c>
+      <c r="B164">
+        <v>100089</v>
+      </c>
+      <c r="C164" t="s">
+        <v>100</v>
+      </c>
+      <c r="D164" s="9">
+        <v>434</v>
+      </c>
+      <c r="E164" t="s">
+        <v>89</v>
+      </c>
+      <c r="F164" t="s">
+        <v>85</v>
+      </c>
+      <c r="G164" s="9">
+        <v>42</v>
+      </c>
+      <c r="H164" s="10">
+        <v>232375</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>90</v>
+      </c>
+      <c r="B165">
+        <v>100090</v>
+      </c>
+      <c r="C165" t="s">
+        <v>101</v>
+      </c>
+      <c r="D165" s="9">
+        <v>431</v>
+      </c>
+      <c r="E165" t="s">
+        <v>91</v>
+      </c>
+      <c r="F165" t="s">
+        <v>85</v>
+      </c>
+      <c r="G165" s="9">
+        <v>33</v>
+      </c>
+      <c r="H165" s="10">
+        <v>49938</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>91</v>
+      </c>
+      <c r="B166">
+        <v>100091</v>
+      </c>
+      <c r="C166" t="s">
+        <v>102</v>
+      </c>
+      <c r="D166" s="9">
+        <v>548</v>
+      </c>
+      <c r="E166" t="s">
+        <v>93</v>
+      </c>
+      <c r="F166" t="s">
+        <v>83</v>
+      </c>
+      <c r="G166" s="9">
+        <v>42</v>
+      </c>
+      <c r="H166" s="10">
+        <v>136016</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>92</v>
+      </c>
+      <c r="B167">
+        <v>100092</v>
+      </c>
+      <c r="C167" t="s">
+        <v>103</v>
+      </c>
+      <c r="D167" s="9">
+        <v>563</v>
+      </c>
+      <c r="E167" t="s">
+        <v>95</v>
+      </c>
+      <c r="F167" t="s">
+        <v>83</v>
+      </c>
+      <c r="G167" s="9">
+        <v>53</v>
+      </c>
+      <c r="H167" s="10">
+        <v>55876</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>93</v>
+      </c>
+      <c r="B168">
+        <v>100093</v>
+      </c>
+      <c r="C168" t="s">
+        <v>104</v>
+      </c>
+      <c r="D168" s="9">
+        <v>714</v>
+      </c>
+      <c r="E168" t="s">
+        <v>89</v>
+      </c>
+      <c r="F168" t="s">
+        <v>85</v>
+      </c>
+      <c r="G168" s="9">
+        <v>21</v>
+      </c>
+      <c r="H168" s="10">
+        <v>201405</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>94</v>
+      </c>
+      <c r="B169">
+        <v>100094</v>
+      </c>
+      <c r="C169" t="s">
+        <v>105</v>
+      </c>
+      <c r="D169" s="9">
+        <v>722</v>
+      </c>
+      <c r="E169" t="s">
+        <v>91</v>
+      </c>
+      <c r="F169" t="s">
+        <v>85</v>
+      </c>
+      <c r="G169" s="9">
+        <v>25</v>
+      </c>
+      <c r="H169" s="10">
+        <v>236344</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>95</v>
+      </c>
+      <c r="B170">
+        <v>100095</v>
+      </c>
+      <c r="C170" t="s">
+        <v>106</v>
+      </c>
+      <c r="D170" s="9">
+        <v>671</v>
+      </c>
+      <c r="E170" t="s">
+        <v>93</v>
+      </c>
+      <c r="F170" t="s">
+        <v>85</v>
+      </c>
+      <c r="G170" s="9">
+        <v>48</v>
+      </c>
+      <c r="H170" s="10">
+        <v>35491</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>96</v>
+      </c>
+      <c r="B171">
+        <v>100096</v>
+      </c>
+      <c r="C171" t="s">
+        <v>107</v>
+      </c>
+      <c r="D171" s="9">
+        <v>434</v>
+      </c>
+      <c r="E171" t="s">
+        <v>95</v>
+      </c>
+      <c r="F171" t="s">
+        <v>85</v>
+      </c>
+      <c r="G171" s="9">
+        <v>37</v>
+      </c>
+      <c r="H171" s="10">
+        <v>14973</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>97</v>
+      </c>
+      <c r="B172">
+        <v>100097</v>
+      </c>
+      <c r="C172" t="s">
+        <v>108</v>
+      </c>
+      <c r="D172" s="9">
+        <v>435</v>
+      </c>
+      <c r="E172" t="s">
+        <v>89</v>
+      </c>
+      <c r="F172" t="s">
+        <v>83</v>
+      </c>
+      <c r="G172" s="9">
+        <v>38</v>
+      </c>
+      <c r="H172" s="10">
+        <v>155262</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>98</v>
+      </c>
+      <c r="B173">
+        <v>100098</v>
+      </c>
+      <c r="C173" t="s">
+        <v>109</v>
+      </c>
+      <c r="D173" s="9">
+        <v>657</v>
+      </c>
+      <c r="E173" t="s">
+        <v>91</v>
+      </c>
+      <c r="F173" t="s">
+        <v>85</v>
+      </c>
+      <c r="G173" s="9">
+        <v>30</v>
+      </c>
+      <c r="H173" s="10">
+        <v>95286</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>99</v>
+      </c>
+      <c r="B174">
+        <v>100099</v>
+      </c>
+      <c r="C174" t="s">
+        <v>110</v>
+      </c>
+      <c r="D174" s="9">
+        <v>682</v>
+      </c>
+      <c r="E174" t="s">
+        <v>93</v>
+      </c>
+      <c r="F174" t="s">
+        <v>85</v>
+      </c>
+      <c r="G174" s="9">
+        <v>30</v>
+      </c>
+      <c r="H174" s="10">
+        <v>100607</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>100</v>
+      </c>
+      <c r="B175">
+        <v>100100</v>
+      </c>
+      <c r="C175" t="s">
+        <v>111</v>
+      </c>
+      <c r="D175" s="9">
+        <v>491</v>
+      </c>
+      <c r="E175" t="s">
+        <v>95</v>
+      </c>
+      <c r="F175" t="s">
+        <v>83</v>
+      </c>
+      <c r="G175" s="9">
+        <v>51</v>
+      </c>
+      <c r="H175" s="10">
+        <v>60230</v>
+      </c>
+    </row>
+    <row r="192" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" spans="5:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" spans="5:7" ht="75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" spans="5:7" ht="90" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="E195" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F195" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="G195" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="196" spans="5:7" ht="88.5" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E196" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G196">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="197" spans="5:7" ht="84" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E197" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="G197">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="198" spans="5:7" ht="87" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E198" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="G198">
+        <v>487584</v>
+      </c>
+    </row>
+    <row r="199" spans="5:7" ht="90.75" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E199" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="G199">
+        <v>6575756</v>
+      </c>
+    </row>
+    <row r="209" spans="5:7" x14ac:dyDescent="0.25">
+      <c r="E209" s="11"/>
+      <c r="F209" s="11"/>
+      <c r="G209" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="G3:H3"/>
+    <mergeCell ref="F29:G29"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="4">
-    <tablePart r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="15">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId14"/>
+    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>